--- a/output/nabos_14_01bavg.xlsx
+++ b/output/nabos_14_01bavg.xlsx
@@ -544,76 +544,76 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1196.752</v>
+        <v>1196.757</v>
       </c>
       <c r="B2" t="n">
         <v>78.14306</v>
       </c>
       <c r="C2" t="n">
-        <v>-172.21511</v>
+        <v>-172.21502</v>
       </c>
       <c r="D2" t="n">
         <v>1213</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0345</v>
+        <v>-0.0348</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0353</v>
+        <v>-0.0356</v>
       </c>
       <c r="G2" t="n">
-        <v>29.467735</v>
+        <v>29.467554</v>
       </c>
       <c r="H2" t="n">
-        <v>29.465423</v>
+        <v>29.465118</v>
       </c>
       <c r="I2" t="n">
-        <v>34.8914</v>
+        <v>34.8916</v>
       </c>
       <c r="J2" t="n">
         <v>34.8893</v>
       </c>
       <c r="K2" t="n">
-        <v>288.386</v>
+        <v>288.412</v>
       </c>
       <c r="L2" t="n">
-        <v>282.663</v>
+        <v>282.345</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1577</v>
+        <v>-0.151</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6668</v>
+        <v>4.6669</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0832</v>
+        <v>0.0829</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0832</v>
+        <v>0.0829</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.019</v>
+        <v>0.0189</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0187</v>
+        <v>0.0189</v>
       </c>
       <c r="S2" t="n">
-        <v>-288</v>
+        <v>-18</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.201</v>
+        <v>-0.0135</v>
       </c>
       <c r="U2" t="n">
         <v>100</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0108</v>
+        <v>2.0109</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7762</v>
+        <v>1.7748</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>456</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -636,76 +636,76 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1197.736</v>
+        <v>1197.74</v>
       </c>
       <c r="B3" t="n">
         <v>78.14302</v>
       </c>
       <c r="C3" t="n">
-        <v>-172.21365</v>
+        <v>-172.21358</v>
       </c>
       <c r="D3" t="n">
         <v>1214</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0359</v>
+        <v>-0.036</v>
       </c>
       <c r="F3" t="n">
         <v>-0.0361</v>
       </c>
       <c r="G3" t="n">
-        <v>29.466967</v>
+        <v>29.466936</v>
       </c>
       <c r="H3" t="n">
-        <v>29.465151</v>
+        <v>29.465186</v>
       </c>
       <c r="I3" t="n">
-        <v>34.8915</v>
+        <v>34.8916</v>
       </c>
       <c r="J3" t="n">
-        <v>34.8893</v>
+        <v>34.8894</v>
       </c>
       <c r="K3" t="n">
-        <v>288.614</v>
+        <v>288.662</v>
       </c>
       <c r="L3" t="n">
-        <v>280.955</v>
+        <v>281.991</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1567</v>
+        <v>-0.1523</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6668</v>
+        <v>4.6669</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0828</v>
+        <v>0.0829</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0828</v>
+        <v>0.0829</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.019</v>
+        <v>0.0189</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0187</v>
+        <v>0.0189</v>
       </c>
       <c r="S3" t="n">
-        <v>4820</v>
+        <v>5085</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3462</v>
+        <v>3.5307</v>
       </c>
       <c r="U3" t="n">
         <v>100</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0118</v>
+        <v>2.012</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7684</v>
+        <v>1.773</v>
       </c>
       <c r="X3" t="n">
-        <v>35</v>
+        <v>711</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -731,49 +731,49 @@
         <v>1198.72</v>
       </c>
       <c r="B4" t="n">
-        <v>78.14287</v>
+        <v>78.14288</v>
       </c>
       <c r="C4" t="n">
-        <v>-172.20947</v>
+        <v>-172.20969</v>
       </c>
       <c r="D4" t="n">
         <v>1215</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0356</v>
+        <v>-0.0358</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0356</v>
+        <v>-0.0358</v>
       </c>
       <c r="G4" t="n">
-        <v>29.467843</v>
+        <v>29.467664</v>
       </c>
       <c r="H4" t="n">
-        <v>29.466071</v>
+        <v>29.465928</v>
       </c>
       <c r="I4" t="n">
         <v>34.8917</v>
       </c>
       <c r="J4" t="n">
-        <v>34.8894</v>
+        <v>34.8895</v>
       </c>
       <c r="K4" t="n">
-        <v>289.12</v>
+        <v>289.009</v>
       </c>
       <c r="L4" t="n">
-        <v>276.882</v>
+        <v>277.38</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1515</v>
+        <v>-0.1519</v>
       </c>
       <c r="N4" t="n">
         <v>4.6669</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0827</v>
+        <v>0.0828</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0827</v>
+        <v>0.0828</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0189</v>
@@ -782,22 +782,22 @@
         <v>0.0189</v>
       </c>
       <c r="S4" t="n">
-        <v>15616</v>
+        <v>15045</v>
       </c>
       <c r="T4" t="n">
-        <v>10.8437</v>
+        <v>10.4471</v>
       </c>
       <c r="U4" t="n">
         <v>100</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0142</v>
+        <v>2.0136</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7502</v>
+        <v>1.7524</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -820,28 +820,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1199.703</v>
+        <v>1199.706</v>
       </c>
       <c r="B5" t="n">
-        <v>78.14289</v>
+        <v>78.1429</v>
       </c>
       <c r="C5" t="n">
-        <v>-172.20966</v>
+        <v>-172.20963</v>
       </c>
       <c r="D5" t="n">
         <v>1216</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0363</v>
+        <v>-0.0362</v>
       </c>
       <c r="F5" t="n">
         <v>-0.0364</v>
       </c>
       <c r="G5" t="n">
-        <v>29.467593</v>
+        <v>29.467658</v>
       </c>
       <c r="H5" t="n">
-        <v>29.465784</v>
+        <v>29.465805</v>
       </c>
       <c r="I5" t="n">
         <v>34.8917</v>
@@ -850,46 +850,46 @@
         <v>34.8894</v>
       </c>
       <c r="K5" t="n">
-        <v>289.118</v>
+        <v>289.102</v>
       </c>
       <c r="L5" t="n">
-        <v>281.111</v>
+        <v>280.847</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1568</v>
+        <v>-0.1529</v>
       </c>
       <c r="N5" t="n">
-        <v>4.667</v>
+        <v>4.6669</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0831</v>
+        <v>0.0829</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0831</v>
+        <v>0.0829</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0189</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0187</v>
+        <v>0.0189</v>
       </c>
       <c r="S5" t="n">
-        <v>15121</v>
+        <v>15224</v>
       </c>
       <c r="T5" t="n">
-        <v>10.5003</v>
+        <v>10.5713</v>
       </c>
       <c r="U5" t="n">
         <v>100</v>
       </c>
       <c r="V5" t="n">
-        <v>2.014</v>
+        <v>2.0139</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7688</v>
+        <v>1.7676</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>385</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -912,76 +912,76 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1200.687</v>
+        <v>1200.697</v>
       </c>
       <c r="B6" t="n">
         <v>78.14294</v>
       </c>
       <c r="C6" t="n">
-        <v>-172.20904</v>
+        <v>-172.2089</v>
       </c>
       <c r="D6" t="n">
         <v>1217</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0372</v>
+        <v>-0.0378</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0382</v>
+        <v>-0.0386</v>
       </c>
       <c r="G6" t="n">
-        <v>29.467134</v>
+        <v>29.466786</v>
       </c>
       <c r="H6" t="n">
-        <v>29.46478</v>
+        <v>29.46448</v>
       </c>
       <c r="I6" t="n">
-        <v>34.8915</v>
+        <v>34.8918</v>
       </c>
       <c r="J6" t="n">
-        <v>34.8895</v>
+        <v>34.8896</v>
       </c>
       <c r="K6" t="n">
-        <v>289.118</v>
+        <v>289.033</v>
       </c>
       <c r="L6" t="n">
-        <v>282.336</v>
+        <v>282.368</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1333</v>
+        <v>-0.1381</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6669</v>
+        <v>4.6671</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0828</v>
+        <v>0.0833</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0828</v>
+        <v>0.0833</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0189</v>
+        <v>0.0187</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0196</v>
+        <v>0.0194</v>
       </c>
       <c r="S6" t="n">
-        <v>16961</v>
+        <v>17437</v>
       </c>
       <c r="T6" t="n">
-        <v>11.7777</v>
+        <v>12.1081</v>
       </c>
       <c r="U6" t="n">
         <v>100</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0137</v>
+        <v>2.0133</v>
       </c>
       <c r="W6" t="n">
-        <v>1.774</v>
+        <v>1.7741</v>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
